--- a/quizzes/peinture-16e-niveau1.xlsx
+++ b/quizzes/peinture-16e-niveau1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\Codex\2026-08-11\referenced-chatgpt-conversation-this-is-an\outputs\quiz-art-excel\fichiers excel terminés\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3FCDD01D-AFB9-49EE-8EDC-974FA51C8574}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F0565818-702E-4C23-8B2F-20CCA60E2DE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="179">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="186">
   <si>
     <t>image</t>
   </si>
@@ -46,6 +46,9 @@
     <t>dimensions</t>
   </si>
   <si>
+    <t>Nationalité</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/b/b5/20171017194217%21D%C3%BCrer_-_Selbstbildnis_im_Pelzrock_-_Alte_Pinakothek.jpg/1920px-20171017194217%21D%C3%BCrer_-_Selbstbildnis_im_Pelzrock_-_Alte_Pinakothek.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr</t>
   </si>
   <si>
@@ -67,6 +70,9 @@
     <t>67 × 49 cm</t>
   </si>
   <si>
+    <t>allemande</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/5/53/Albrecht_D%C3%BCrer_-_Adorazione_dei_Magi_-_Google_Art_Project.jpg/1280px-Albrecht_D%C3%BCrer_-_Adorazione_dei_Magi_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
@@ -100,6 +106,9 @@
     <t>95 × 85 cm</t>
   </si>
   <si>
+    <t>italienne</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/7/78/Judith_Beheading_Holofernes_-_Caravaggio.jpg/1280px-Judith_Beheading_Holofernes_-_Caravaggio.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr</t>
   </si>
   <si>
@@ -133,6 +142,9 @@
     <t>480 × 360 cm</t>
   </si>
   <si>
+    <t>grecque</t>
+  </si>
+  <si>
     <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/7/7f/El_caballero_de_la_mano_en_el_pecho%2C_by_El_Greco%2C_from_Prado_in_Google_Earth.jpg/960px-El_caballero_de_la_mano_en_el_pecho%2C_by_El_Greco%2C_from_Prado_in_Google_Earth.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
@@ -301,6 +313,9 @@
     <t>131,5 × 119 cm</t>
   </si>
   <si>
+    <t>hollandaise (Pays-Bas)</t>
+  </si>
+  <si>
     <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/4/4c/Jheronimus_Bosch_-_De_hooiwagen_%28c.1516%2C_Prado%29.jpg/1280px-Jheronimus_Bosch_-_De_hooiwagen_%28c.1516%2C_Prado%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
@@ -334,6 +349,9 @@
     <t>96 × 74 cm</t>
   </si>
   <si>
+    <t>française</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/6/6b/Parmigianino_-_Madonna_dal_collo_lungo_-_Google_Art_Project.jpg/1280px-Parmigianino_-_Madonna_dal_collo_lungo_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
@@ -499,6 +517,9 @@
     <t>114 × 155 cm</t>
   </si>
   <si>
+    <t>flamande (Belgique)</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/c/c3/Raphael_School_of_Athens.jpg/1280px-Raphael_School_of_Athens.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
@@ -511,6 +532,9 @@
     <t>Chambre de la Signature, Vatican</t>
   </si>
   <si>
+    <t xml:space="preserve">L'École d'Athènes </t>
+  </si>
+  <si>
     <t>1483-1520</t>
   </si>
   <si>
@@ -554,9 +578,6 @@
   </si>
   <si>
     <t>677 × 994 cm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L'École d'Athènes </t>
   </si>
 </sst>
 </file>
@@ -1044,7 +1065,9 @@
       <c r="H1" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="11"/>
+      <c r="I1" s="11" t="s">
+        <v>8</v>
+      </c>
       <c r="J1" s="11"/>
       <c r="K1" s="11"/>
       <c r="L1" s="11"/>
@@ -1058,706 +1081,786 @@
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C2" s="13">
         <v>1500</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E2" s="14" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="I2" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C3" s="13">
         <v>1504</v>
       </c>
       <c r="D3" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I3" t="s">
         <v>16</v>
-      </c>
-      <c r="E3" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="F3" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G3" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="H3" s="5" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C4" s="13">
         <v>1598</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E4" s="14" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>25</v>
+        <v>27</v>
+      </c>
+      <c r="I4" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C5" s="13">
         <v>1599</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="E5" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="I5" t="s">
         <v>28</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="G5" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="H5" s="5" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E6" s="14" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>36</v>
+        <v>39</v>
+      </c>
+      <c r="I6" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C7" s="13">
         <v>1580</v>
       </c>
       <c r="D7" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="E7" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="F7" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="E7" s="14" t="s">
-        <v>39</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>35</v>
-      </c>
       <c r="G7" s="5" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H7" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="I7" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C8" s="13" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="E8" s="14" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>47</v>
+        <v>51</v>
+      </c>
+      <c r="I8" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C9" s="13" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="D9" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="E9" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="F9" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="E9" s="14" t="s">
-        <v>51</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>46</v>
-      </c>
       <c r="G9" s="5" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>52</v>
+        <v>56</v>
+      </c>
+      <c r="I9" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="C10" s="13" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="E10" s="14" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>60</v>
+        <v>64</v>
+      </c>
+      <c r="I10" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="11" spans="1:19" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="C11" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="E11" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="F11" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="D11" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="E11" s="14" t="s">
-        <v>63</v>
-      </c>
-      <c r="F11" s="5" t="s">
-        <v>58</v>
-      </c>
       <c r="G11" s="5" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>65</v>
+        <v>69</v>
+      </c>
+      <c r="I11" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="C12" s="13">
         <v>1573</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="E12" s="14" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>71</v>
+        <v>75</v>
+      </c>
+      <c r="I12" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="C13" s="13">
         <v>1573</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="E13" s="14" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>71</v>
+        <v>75</v>
+      </c>
+      <c r="I13" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C14" s="13" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="E14" s="14" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>80</v>
+        <v>84</v>
+      </c>
+      <c r="I14" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C15" s="13" t="s">
+        <v>86</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="E15" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="F15" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="D15" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="E15" s="14" t="s">
-        <v>84</v>
-      </c>
-      <c r="F15" s="5" t="s">
-        <v>78</v>
-      </c>
       <c r="G15" s="5" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="H15" s="5" t="s">
-        <v>86</v>
+        <v>90</v>
+      </c>
+      <c r="I15" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="C16" s="13">
         <v>1501</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="E16" s="14" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="H16" s="5" t="s">
-        <v>92</v>
+        <v>96</v>
+      </c>
+      <c r="I16" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="C17" s="13">
         <v>1516</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="E17" s="14" t="s">
+        <v>99</v>
+      </c>
+      <c r="F17" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="F17" s="5" t="s">
-        <v>90</v>
-      </c>
       <c r="G17" s="5" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>96</v>
+        <v>101</v>
+      </c>
+      <c r="I17" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="18" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="C18" s="13" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="E18" s="14" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="H18" s="5" t="s">
-        <v>103</v>
+        <v>108</v>
+      </c>
+      <c r="I18" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="19" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="C19" s="13" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E19" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="G19" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="F19" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="G19" s="5" t="s">
-        <v>102</v>
-      </c>
       <c r="H19" s="5" t="s">
-        <v>109</v>
+        <v>115</v>
+      </c>
+      <c r="I19" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="20" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="C20" s="13" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="E20" s="14" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H20" s="5" t="s">
-        <v>115</v>
+        <v>121</v>
+      </c>
+      <c r="I20" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="21" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="C21" s="13" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="E21" s="14" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H21" s="5" t="s">
-        <v>119</v>
+        <v>125</v>
+      </c>
+      <c r="I21" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="22" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="C22" s="13" t="s">
+        <v>127</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="E22" s="14" t="s">
+        <v>129</v>
+      </c>
+      <c r="F22" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="B22" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="C22" s="13" t="s">
-        <v>121</v>
-      </c>
-      <c r="D22" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="E22" s="14" t="s">
-        <v>123</v>
-      </c>
-      <c r="F22" s="5" t="s">
-        <v>114</v>
-      </c>
       <c r="G22" s="5" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H22" s="5" t="s">
-        <v>124</v>
+        <v>130</v>
+      </c>
+      <c r="I22" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="23" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="C23" s="13" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="E23" s="14" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="H23" s="5" t="s">
-        <v>131</v>
+        <v>137</v>
+      </c>
+      <c r="I23" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="24" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="C24" s="13" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="E24" s="14" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H24" s="5" t="s">
-        <v>137</v>
+        <v>143</v>
+      </c>
+      <c r="I24" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="25" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A25" s="6" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="C25" s="13" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="E25" s="14" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="H25" s="5" t="s">
-        <v>140</v>
+        <v>146</v>
+      </c>
+      <c r="I25" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="26" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A26" s="6" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="C26" s="13" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="E26" s="14" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="H26" s="5" t="s">
-        <v>148</v>
+        <v>154</v>
+      </c>
+      <c r="I26" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="27" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A27" s="6" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="C27" s="13" t="s">
+        <v>156</v>
+      </c>
+      <c r="D27" s="5" t="s">
         <v>150</v>
       </c>
-      <c r="D27" s="5" t="s">
-        <v>144</v>
-      </c>
       <c r="E27" s="14" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="H27" s="5" t="s">
-        <v>152</v>
+        <v>158</v>
+      </c>
+      <c r="I27" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="28" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="6" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="C28" s="7">
         <v>1563</v>
       </c>
       <c r="D28" s="15" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="E28" s="8" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="F28" s="5" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="G28" s="5" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="H28" s="5" t="s">
-        <v>158</v>
-      </c>
-      <c r="I28" s="2"/>
+        <v>164</v>
+      </c>
+      <c r="I28" s="2" t="s">
+        <v>165</v>
+      </c>
       <c r="J28" s="2"/>
       <c r="K28" s="2"/>
       <c r="L28" s="2"/>
@@ -1771,30 +1874,32 @@
     </row>
     <row r="29" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="C29" s="13" t="s">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="E29" s="14" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="F29" s="5" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="H29" s="5" t="s">
-        <v>164</v>
-      </c>
-      <c r="I29" s="2"/>
+        <v>172</v>
+      </c>
+      <c r="I29" s="2" t="s">
+        <v>28</v>
+      </c>
       <c r="J29" s="2"/>
       <c r="K29" s="2"/>
       <c r="L29" s="2"/>
@@ -1808,54 +1913,60 @@
     </row>
     <row r="30" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="C30" s="13" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="E30" s="14" t="s">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="F30" s="5" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="G30" s="5" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H30" s="5" t="s">
-        <v>171</v>
+        <v>179</v>
+      </c>
+      <c r="I30" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="31" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="C31" s="13" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="E31" s="14" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="F31" s="5" t="s">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="G31" s="5" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H31" s="5" t="s">
-        <v>177</v>
+        <v>185</v>
+      </c>
+      <c r="I31" t="s">
+        <v>28</v>
       </c>
     </row>
   </sheetData>
